--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F507"/>
+  <dimension ref="A1:F511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -798,7 +798,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-011</t>
+          <t>TC-AUTH-010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 11: Mobile credential security scenario 11</t>
+          <t>Mobile auth validation 10: Sign-in screen escape handling</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-012</t>
+          <t>TC-AUTH-011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 12: Mobile credential security scenario 12</t>
+          <t>Mobile auth validation 11: Mobile credential security scenario 11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-013</t>
+          <t>TC-AUTH-012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 13: Mobile credential security scenario 13</t>
+          <t>Mobile auth validation 12: Mobile credential security scenario 12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-014</t>
+          <t>TC-AUTH-013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 14: Mobile credential security scenario 14</t>
+          <t>Mobile auth validation 13: Mobile credential security scenario 13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-015</t>
+          <t>TC-AUTH-014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 15: Mobile credential security scenario 15</t>
+          <t>Mobile auth validation 14: Mobile credential security scenario 14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-016</t>
+          <t>TC-AUTH-015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 16: Mobile credential security scenario 16</t>
+          <t>Mobile auth validation 15: Mobile credential security scenario 15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-017</t>
+          <t>TC-AUTH-016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 17: Mobile credential security scenario 17</t>
+          <t>Mobile auth validation 16: Mobile credential security scenario 16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-018</t>
+          <t>TC-AUTH-017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 18: Mobile credential security scenario 18</t>
+          <t>Mobile auth validation 17: Mobile credential security scenario 17</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-019</t>
+          <t>TC-AUTH-018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 19: Mobile credential security scenario 19</t>
+          <t>Mobile auth validation 18: Mobile credential security scenario 18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-020</t>
+          <t>TC-AUTH-019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 20: Mobile credential security scenario 20</t>
+          <t>Mobile auth validation 19: Mobile credential security scenario 19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-021</t>
+          <t>TC-AUTH-020</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 21: Mobile credential security scenario 21</t>
+          <t>Mobile auth validation 20: Mobile credential security scenario 20</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-022</t>
+          <t>TC-AUTH-021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 22: Mobile credential security scenario 22</t>
+          <t>Mobile auth validation 21: Mobile credential security scenario 21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-023</t>
+          <t>TC-AUTH-022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 23: Mobile credential security scenario 23</t>
+          <t>Mobile auth validation 22: Mobile credential security scenario 22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-024</t>
+          <t>TC-AUTH-023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 24: Mobile credential security scenario 24</t>
+          <t>Mobile auth validation 23: Mobile credential security scenario 23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-025</t>
+          <t>TC-AUTH-024</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 25: Mobile credential security scenario 25</t>
+          <t>Mobile auth validation 24: Mobile credential security scenario 24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-026</t>
+          <t>TC-AUTH-025</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 26: Mobile credential security scenario 26</t>
+          <t>Mobile auth validation 25: Mobile credential security scenario 25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-027</t>
+          <t>TC-AUTH-026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 27: Mobile credential security scenario 27</t>
+          <t>Mobile auth validation 26: Mobile credential security scenario 26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-028</t>
+          <t>TC-AUTH-027</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 28: Mobile credential security scenario 28</t>
+          <t>Mobile auth validation 27: Mobile credential security scenario 27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-029</t>
+          <t>TC-AUTH-028</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 29: Mobile credential security scenario 29</t>
+          <t>Mobile auth validation 28: Mobile credential security scenario 28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-030</t>
+          <t>TC-AUTH-029</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 30: Mobile credential security scenario 30</t>
+          <t>Mobile auth validation 29: Mobile credential security scenario 29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-031</t>
+          <t>TC-AUTH-030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 31: Mobile credential security scenario 31</t>
+          <t>Mobile auth validation 30: Mobile credential security scenario 30</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-032</t>
+          <t>TC-AUTH-031</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 32: Mobile credential security scenario 32</t>
+          <t>Mobile auth validation 31: Mobile credential security scenario 31</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-033</t>
+          <t>TC-AUTH-032</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 33: Mobile credential security scenario 33</t>
+          <t>Mobile auth validation 32: Mobile credential security scenario 32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-034</t>
+          <t>TC-AUTH-033</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 34: Mobile credential security scenario 34</t>
+          <t>Mobile auth validation 33: Mobile credential security scenario 33</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-035</t>
+          <t>TC-AUTH-034</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 35: Mobile credential security scenario 35</t>
+          <t>Mobile auth validation 34: Mobile credential security scenario 34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-036</t>
+          <t>TC-AUTH-035</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 36: Mobile credential security scenario 36</t>
+          <t>Mobile auth validation 35: Mobile credential security scenario 35</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-037</t>
+          <t>TC-AUTH-036</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 37: Mobile credential security scenario 37</t>
+          <t>Mobile auth validation 36: Mobile credential security scenario 36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-038</t>
+          <t>TC-AUTH-037</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 38: Mobile credential security scenario 38</t>
+          <t>Mobile auth validation 37: Mobile credential security scenario 37</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-039</t>
+          <t>TC-AUTH-038</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 39: Mobile credential security scenario 39</t>
+          <t>Mobile auth validation 38: Mobile credential security scenario 38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTH-040</t>
+          <t>TC-AUTH-039</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mobile auth validation 40: Mobile credential security scenario 40</t>
+          <t>Mobile auth validation 39: Mobile credential security scenario 39</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1758,22 +1758,22 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-001</t>
+          <t>TC-AUTH-040</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 1: Guest access restriction to private user profile</t>
+          <t>Mobile auth validation 40: Mobile credential security scenario 40</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1790,7 +1790,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-002</t>
+          <t>TC-AUTZ-001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 2: Protected report history route gate</t>
+          <t>Role-based access scenario 1: Guest access restriction to private user profile</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-003</t>
+          <t>TC-AUTZ-002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 3: Authenticated clinical dashboard access</t>
+          <t>Role-based access scenario 2: Protected report history route gate</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-004</t>
+          <t>TC-AUTZ-003</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 4: Read-only demonstration state enforcement</t>
+          <t>Role-based access scenario 3: Authenticated clinical dashboard access</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-005</t>
+          <t>TC-AUTZ-004</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 5: Token expiration redirect enforcement</t>
+          <t>Role-based access scenario 4: Read-only demonstration state enforcement</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-006</t>
+          <t>TC-AUTZ-005</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 6: Authorization boundary scenario 6</t>
+          <t>Role-based access scenario 5: Token expiration redirect enforcement</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -1950,7 +1950,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-007</t>
+          <t>TC-AUTZ-006</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 7: Authorization boundary scenario 7</t>
+          <t>Role-based access scenario 6: Authorization boundary scenario 6</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-008</t>
+          <t>TC-AUTZ-007</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 8: Authorization boundary scenario 8</t>
+          <t>Role-based access scenario 7: Authorization boundary scenario 7</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-009</t>
+          <t>TC-AUTZ-008</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 9: Authorization boundary scenario 9</t>
+          <t>Role-based access scenario 8: Authorization boundary scenario 8</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-010</t>
+          <t>TC-AUTZ-009</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 10: Authorization boundary scenario 10</t>
+          <t>Role-based access scenario 9: Authorization boundary scenario 9</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-011</t>
+          <t>TC-AUTZ-010</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 11: Authorization boundary scenario 11</t>
+          <t>Role-based access scenario 10: Authorization boundary scenario 10</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-012</t>
+          <t>TC-AUTZ-011</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 12: Authorization boundary scenario 12</t>
+          <t>Role-based access scenario 11: Authorization boundary scenario 11</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-013</t>
+          <t>TC-AUTZ-012</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 13: Authorization boundary scenario 13</t>
+          <t>Role-based access scenario 12: Authorization boundary scenario 12</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-014</t>
+          <t>TC-AUTZ-013</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 14: Authorization boundary scenario 14</t>
+          <t>Role-based access scenario 13: Authorization boundary scenario 13</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-015</t>
+          <t>TC-AUTZ-014</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 15: Authorization boundary scenario 15</t>
+          <t>Role-based access scenario 14: Authorization boundary scenario 14</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-016</t>
+          <t>TC-AUTZ-015</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 16: Authorization boundary scenario 16</t>
+          <t>Role-based access scenario 15: Authorization boundary scenario 15</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-017</t>
+          <t>TC-AUTZ-016</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 17: Authorization boundary scenario 17</t>
+          <t>Role-based access scenario 16: Authorization boundary scenario 16</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-018</t>
+          <t>TC-AUTZ-017</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 18: Authorization boundary scenario 18</t>
+          <t>Role-based access scenario 17: Authorization boundary scenario 17</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2334,7 +2334,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-019</t>
+          <t>TC-AUTZ-018</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 19: Authorization boundary scenario 19</t>
+          <t>Role-based access scenario 18: Authorization boundary scenario 18</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-020</t>
+          <t>TC-AUTZ-019</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 20: Authorization boundary scenario 20</t>
+          <t>Role-based access scenario 19: Authorization boundary scenario 19</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-021</t>
+          <t>TC-AUTZ-020</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 21: Authorization boundary scenario 21</t>
+          <t>Role-based access scenario 20: Authorization boundary scenario 20</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-022</t>
+          <t>TC-AUTZ-021</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 22: Authorization boundary scenario 22</t>
+          <t>Role-based access scenario 21: Authorization boundary scenario 21</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-023</t>
+          <t>TC-AUTZ-022</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 23: Authorization boundary scenario 23</t>
+          <t>Role-based access scenario 22: Authorization boundary scenario 22</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-024</t>
+          <t>TC-AUTZ-023</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 24: Authorization boundary scenario 24</t>
+          <t>Role-based access scenario 23: Authorization boundary scenario 23</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-025</t>
+          <t>TC-AUTZ-024</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 25: Authorization boundary scenario 25</t>
+          <t>Role-based access scenario 24: Authorization boundary scenario 24</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-026</t>
+          <t>TC-AUTZ-025</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 26: Authorization boundary scenario 26</t>
+          <t>Role-based access scenario 25: Authorization boundary scenario 25</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-027</t>
+          <t>TC-AUTZ-026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 27: Authorization boundary scenario 27</t>
+          <t>Role-based access scenario 26: Authorization boundary scenario 26</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-028</t>
+          <t>TC-AUTZ-027</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 28: Authorization boundary scenario 28</t>
+          <t>Role-based access scenario 27: Authorization boundary scenario 27</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2654,7 +2654,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-029</t>
+          <t>TC-AUTZ-028</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 29: Authorization boundary scenario 29</t>
+          <t>Role-based access scenario 28: Authorization boundary scenario 28</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TC-AUTZ-030</t>
+          <t>TC-AUTZ-029</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Role-based access scenario 30: Authorization boundary scenario 30</t>
+          <t>Role-based access scenario 29: Authorization boundary scenario 29</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2718,17 +2718,17 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-001</t>
+          <t>TC-AUTZ-030</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 1: Valid new user onboarding</t>
+          <t>Role-based access scenario 30: Authorization boundary scenario 30</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-002</t>
+          <t>TC-REG-001</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 2: Duplicate email conflict handling</t>
+          <t>Patient registration scenario 1: Valid new user onboarding</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-003</t>
+          <t>TC-REG-002</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 3: Weak password complexity rejection</t>
+          <t>Patient registration scenario 2: Duplicate email conflict handling</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-004</t>
+          <t>TC-REG-003</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 4: Terms of service acceptance checkbox</t>
+          <t>Patient registration scenario 3: Weak password complexity rejection</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-005</t>
+          <t>TC-REG-004</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 5: Registration verification flow 5</t>
+          <t>Patient registration scenario 4: Terms of service acceptance checkbox</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-006</t>
+          <t>TC-REG-005</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 6: Registration verification flow 6</t>
+          <t>Patient registration scenario 5: Registration verification flow 5</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-007</t>
+          <t>TC-REG-006</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 7: Registration verification flow 7</t>
+          <t>Patient registration scenario 6: Registration verification flow 6</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-008</t>
+          <t>TC-REG-007</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 8: Registration verification flow 8</t>
+          <t>Patient registration scenario 7: Registration verification flow 7</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-009</t>
+          <t>TC-REG-008</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 9: Registration verification flow 9</t>
+          <t>Patient registration scenario 8: Registration verification flow 8</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-010</t>
+          <t>TC-REG-009</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 10: Registration verification flow 10</t>
+          <t>Patient registration scenario 9: Registration verification flow 9</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-011</t>
+          <t>TC-REG-010</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 11: Registration verification flow 11</t>
+          <t>Patient registration scenario 10: Registration verification flow 10</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-012</t>
+          <t>TC-REG-011</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 12: Registration verification flow 12</t>
+          <t>Patient registration scenario 11: Registration verification flow 11</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-013</t>
+          <t>TC-REG-012</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 13: Registration verification flow 13</t>
+          <t>Patient registration scenario 12: Registration verification flow 12</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-014</t>
+          <t>TC-REG-013</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 14: Registration verification flow 14</t>
+          <t>Patient registration scenario 13: Registration verification flow 13</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-015</t>
+          <t>TC-REG-014</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 15: Registration verification flow 15</t>
+          <t>Patient registration scenario 14: Registration verification flow 14</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-016</t>
+          <t>TC-REG-015</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 16: Registration verification flow 16</t>
+          <t>Patient registration scenario 15: Registration verification flow 15</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-017</t>
+          <t>TC-REG-016</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 17: Registration verification flow 17</t>
+          <t>Patient registration scenario 16: Registration verification flow 16</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-018</t>
+          <t>TC-REG-017</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 18: Registration verification flow 18</t>
+          <t>Patient registration scenario 17: Registration verification flow 17</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-019</t>
+          <t>TC-REG-018</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 19: Registration verification flow 19</t>
+          <t>Patient registration scenario 18: Registration verification flow 18</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-REG-020</t>
+          <t>TC-REG-019</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Patient registration scenario 20: Registration verification flow 20</t>
+          <t>Patient registration scenario 19: Registration verification flow 19</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3358,22 +3358,22 @@
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-001</t>
+          <t>TC-REG-020</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Profile Management</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 1: Update age and gender baseline</t>
+          <t>Patient registration scenario 20: Registration verification flow 20</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3390,7 +3390,7 @@
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-002</t>
+          <t>TC-PROF-001</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 2: Add pre-existing conditions</t>
+          <t>Profile setting scenario 1: Update age and gender baseline</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-003</t>
+          <t>TC-PROF-002</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 3: Toggle offline inference mode</t>
+          <t>Profile setting scenario 2: Add pre-existing conditions</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-004</t>
+          <t>TC-PROF-003</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 4: Change profile picture</t>
+          <t>Profile setting scenario 3: Toggle offline inference mode</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-005</t>
+          <t>TC-PROF-004</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 5: Profile preference scenario 5</t>
+          <t>Profile setting scenario 4: Change profile picture</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-006</t>
+          <t>TC-PROF-005</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 6: Profile preference scenario 6</t>
+          <t>Profile setting scenario 5: Profile preference scenario 5</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-007</t>
+          <t>TC-PROF-006</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 7: Profile preference scenario 7</t>
+          <t>Profile setting scenario 6: Profile preference scenario 6</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-008</t>
+          <t>TC-PROF-007</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 8: Profile preference scenario 8</t>
+          <t>Profile setting scenario 7: Profile preference scenario 7</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-009</t>
+          <t>TC-PROF-008</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 9: Profile preference scenario 9</t>
+          <t>Profile setting scenario 8: Profile preference scenario 8</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-010</t>
+          <t>TC-PROF-009</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 10: Profile preference scenario 10</t>
+          <t>Profile setting scenario 9: Profile preference scenario 9</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-011</t>
+          <t>TC-PROF-010</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 11: Profile preference scenario 11</t>
+          <t>Profile setting scenario 10: Profile preference scenario 10</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-012</t>
+          <t>TC-PROF-011</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 12: Profile preference scenario 12</t>
+          <t>Profile setting scenario 11: Profile preference scenario 11</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-013</t>
+          <t>TC-PROF-012</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 13: Profile preference scenario 13</t>
+          <t>Profile setting scenario 12: Profile preference scenario 12</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-014</t>
+          <t>TC-PROF-013</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 14: Profile preference scenario 14</t>
+          <t>Profile setting scenario 13: Profile preference scenario 13</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-015</t>
+          <t>TC-PROF-014</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 15: Profile preference scenario 15</t>
+          <t>Profile setting scenario 14: Profile preference scenario 14</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-016</t>
+          <t>TC-PROF-015</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 16: Profile preference scenario 16</t>
+          <t>Profile setting scenario 15: Profile preference scenario 15</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-017</t>
+          <t>TC-PROF-016</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 17: Profile preference scenario 17</t>
+          <t>Profile setting scenario 16: Profile preference scenario 16</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-018</t>
+          <t>TC-PROF-017</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 18: Profile preference scenario 18</t>
+          <t>Profile setting scenario 17: Profile preference scenario 17</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-019</t>
+          <t>TC-PROF-018</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 19: Profile preference scenario 19</t>
+          <t>Profile setting scenario 18: Profile preference scenario 18</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-PROF-020</t>
+          <t>TC-PROF-019</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Profile setting scenario 20: Profile preference scenario 20</t>
+          <t>Profile setting scenario 19: Profile preference scenario 19</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -3998,22 +3998,22 @@
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-001</t>
+          <t>TC-PROF-020</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Profile Management</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 1: Bottom bar Dashboard to Upload transition</t>
+          <t>Profile setting scenario 20: Profile preference scenario 20</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -4030,7 +4030,7 @@
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-002</t>
+          <t>TC-NAV-001</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 2: Bottom bar Dashboard to Chat transition</t>
+          <t>App navigation route 1: Bottom bar Dashboard to Upload transition</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-003</t>
+          <t>TC-NAV-002</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 3: Bottom bar Dashboard to Profile transition</t>
+          <t>App navigation route 2: Bottom bar Dashboard to Chat transition</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-004</t>
+          <t>TC-NAV-003</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 4: Hardware back button behavior on Android</t>
+          <t>App navigation route 3: Bottom bar Dashboard to Profile transition</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-005</t>
+          <t>TC-NAV-004</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 5: Deep-link route resolution</t>
+          <t>App navigation route 4: Hardware back button behavior on Android</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-006</t>
+          <t>TC-NAV-005</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 6: Screen navigation transition 6</t>
+          <t>App navigation route 5: Deep-link route resolution</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-007</t>
+          <t>TC-NAV-006</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 7: Screen navigation transition 7</t>
+          <t>App navigation route 6: Screen navigation transition 6</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-008</t>
+          <t>TC-NAV-007</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 8: Screen navigation transition 8</t>
+          <t>App navigation route 7: Screen navigation transition 7</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-009</t>
+          <t>TC-NAV-008</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 9: Screen navigation transition 9</t>
+          <t>App navigation route 8: Screen navigation transition 8</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-010</t>
+          <t>TC-NAV-009</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 10: Screen navigation transition 10</t>
+          <t>App navigation route 9: Screen navigation transition 9</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-011</t>
+          <t>TC-NAV-010</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 11: Screen navigation transition 11</t>
+          <t>App navigation route 10: Screen navigation transition 10</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-012</t>
+          <t>TC-NAV-011</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 12: Screen navigation transition 12</t>
+          <t>App navigation route 11: Screen navigation transition 11</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-013</t>
+          <t>TC-NAV-012</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 13: Screen navigation transition 13</t>
+          <t>App navigation route 12: Screen navigation transition 12</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-014</t>
+          <t>TC-NAV-013</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 14: Screen navigation transition 14</t>
+          <t>App navigation route 13: Screen navigation transition 13</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-015</t>
+          <t>TC-NAV-014</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 15: Screen navigation transition 15</t>
+          <t>App navigation route 14: Screen navigation transition 14</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-016</t>
+          <t>TC-NAV-015</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 16: Screen navigation transition 16</t>
+          <t>App navigation route 15: Screen navigation transition 15</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-017</t>
+          <t>TC-NAV-016</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 17: Screen navigation transition 17</t>
+          <t>App navigation route 16: Screen navigation transition 16</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-018</t>
+          <t>TC-NAV-017</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 18: Screen navigation transition 18</t>
+          <t>App navigation route 17: Screen navigation transition 17</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-019</t>
+          <t>TC-NAV-018</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 19: Screen navigation transition 19</t>
+          <t>App navigation route 18: Screen navigation transition 18</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-020</t>
+          <t>TC-NAV-019</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 20: Screen navigation transition 20</t>
+          <t>App navigation route 19: Screen navigation transition 19</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-021</t>
+          <t>TC-NAV-020</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 21: Screen navigation transition 21</t>
+          <t>App navigation route 20: Screen navigation transition 20</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-022</t>
+          <t>TC-NAV-021</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 22: Screen navigation transition 22</t>
+          <t>App navigation route 21: Screen navigation transition 21</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-023</t>
+          <t>TC-NAV-022</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 23: Screen navigation transition 23</t>
+          <t>App navigation route 22: Screen navigation transition 22</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-024</t>
+          <t>TC-NAV-023</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 24: Screen navigation transition 24</t>
+          <t>App navigation route 23: Screen navigation transition 23</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-025</t>
+          <t>TC-NAV-024</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 25: Screen navigation transition 25</t>
+          <t>App navigation route 24: Screen navigation transition 24</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-026</t>
+          <t>TC-NAV-025</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 26: Screen navigation transition 26</t>
+          <t>App navigation route 25: Screen navigation transition 25</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-027</t>
+          <t>TC-NAV-026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 27: Screen navigation transition 27</t>
+          <t>App navigation route 26: Screen navigation transition 26</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-028</t>
+          <t>TC-NAV-027</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 28: Screen navigation transition 28</t>
+          <t>App navigation route 27: Screen navigation transition 27</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-029</t>
+          <t>TC-NAV-028</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 29: Screen navigation transition 29</t>
+          <t>App navigation route 28: Screen navigation transition 28</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TC-NAV-030</t>
+          <t>TC-NAV-029</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>App navigation route 30: Screen navigation transition 30</t>
+          <t>App navigation route 29: Screen navigation transition 29</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -4958,22 +4958,22 @@
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-001</t>
+          <t>TC-NAV-030</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 1: Header brand title visibility</t>
+          <t>App navigation route 30: Screen navigation transition 30</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-002</t>
+          <t>TC-DASH-001</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 2: Summary report card display</t>
+          <t>Dashboard widget validation 1: Header brand title visibility</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-003</t>
+          <t>TC-DASH-002</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 3: Recent biomarker trends chart</t>
+          <t>Dashboard widget validation 2: Summary report card display</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-004</t>
+          <t>TC-DASH-003</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 4: Quick action upload button</t>
+          <t>Dashboard widget validation 3: Recent biomarker trends chart</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-005</t>
+          <t>TC-DASH-004</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 5: Dashboard component check 5</t>
+          <t>Dashboard widget validation 4: Quick action upload button</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-006</t>
+          <t>TC-DASH-005</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 6: Dashboard component check 6</t>
+          <t>Dashboard widget validation 5: Dashboard component check 5</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-007</t>
+          <t>TC-DASH-006</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 7: Dashboard component check 7</t>
+          <t>Dashboard widget validation 6: Dashboard component check 6</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-008</t>
+          <t>TC-DASH-007</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 8: Dashboard component check 8</t>
+          <t>Dashboard widget validation 7: Dashboard component check 7</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-009</t>
+          <t>TC-DASH-008</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 9: Dashboard component check 9</t>
+          <t>Dashboard widget validation 8: Dashboard component check 8</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-010</t>
+          <t>TC-DASH-009</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 10: Dashboard component check 10</t>
+          <t>Dashboard widget validation 9: Dashboard component check 9</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-011</t>
+          <t>TC-DASH-010</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 11: Dashboard component check 11</t>
+          <t>Dashboard widget validation 10: Dashboard component check 10</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-012</t>
+          <t>TC-DASH-011</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 12: Dashboard component check 12</t>
+          <t>Dashboard widget validation 11: Dashboard component check 11</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-013</t>
+          <t>TC-DASH-012</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 13: Dashboard component check 13</t>
+          <t>Dashboard widget validation 12: Dashboard component check 12</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-014</t>
+          <t>TC-DASH-013</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 14: Dashboard component check 14</t>
+          <t>Dashboard widget validation 13: Dashboard component check 13</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-015</t>
+          <t>TC-DASH-014</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 15: Dashboard component check 15</t>
+          <t>Dashboard widget validation 14: Dashboard component check 14</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-016</t>
+          <t>TC-DASH-015</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 16: Dashboard component check 16</t>
+          <t>Dashboard widget validation 15: Dashboard component check 15</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-017</t>
+          <t>TC-DASH-016</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 17: Dashboard component check 17</t>
+          <t>Dashboard widget validation 16: Dashboard component check 16</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-018</t>
+          <t>TC-DASH-017</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 18: Dashboard component check 18</t>
+          <t>Dashboard widget validation 17: Dashboard component check 17</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-019</t>
+          <t>TC-DASH-018</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 19: Dashboard component check 19</t>
+          <t>Dashboard widget validation 18: Dashboard component check 18</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TC-DASH-020</t>
+          <t>TC-DASH-019</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Dashboard widget validation 20: Dashboard component check 20</t>
+          <t>Dashboard widget validation 19: Dashboard component check 19</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5598,22 +5598,22 @@
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-001</t>
+          <t>TC-DASH-020</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 1: Text report paste area input</t>
+          <t>Dashboard widget validation 20: Dashboard component check 20</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -5630,7 +5630,7 @@
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-002</t>
+          <t>TC-FORM-001</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 2: Form clear and reset button</t>
+          <t>Form interaction scenario 1: Text report paste area input</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-003</t>
+          <t>TC-FORM-002</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 3: Long text buffer auto-wrapping</t>
+          <t>Form interaction scenario 2: Form clear and reset button</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-004</t>
+          <t>TC-FORM-003</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 4: Keyboard hide on touch outside</t>
+          <t>Form interaction scenario 3: Long text buffer auto-wrapping</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-005</t>
+          <t>TC-FORM-004</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 5: Form field state validation 5</t>
+          <t>Form interaction scenario 4: Keyboard hide on touch outside</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-006</t>
+          <t>TC-FORM-005</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 6: Form field state validation 6</t>
+          <t>Form interaction scenario 5: Form field state validation 5</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-007</t>
+          <t>TC-FORM-006</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 7: Form field state validation 7</t>
+          <t>Form interaction scenario 6: Form field state validation 6</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-009</t>
+          <t>TC-FORM-007</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 9: Form field state validation 9</t>
+          <t>Form interaction scenario 7: Form field state validation 7</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-010</t>
+          <t>TC-FORM-008</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 10: Form field state validation 10</t>
+          <t>Form interaction scenario 8: Form field state validation 8</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-011</t>
+          <t>TC-FORM-009</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 11: Form field state validation 11</t>
+          <t>Form interaction scenario 9: Form field state validation 9</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-012</t>
+          <t>TC-FORM-010</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 12: Form field state validation 12</t>
+          <t>Form interaction scenario 10: Form field state validation 10</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-013</t>
+          <t>TC-FORM-011</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 13: Form field state validation 13</t>
+          <t>Form interaction scenario 11: Form field state validation 11</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-014</t>
+          <t>TC-FORM-012</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 14: Form field state validation 14</t>
+          <t>Form interaction scenario 12: Form field state validation 12</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-015</t>
+          <t>TC-FORM-013</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 15: Form field state validation 15</t>
+          <t>Form interaction scenario 13: Form field state validation 13</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-016</t>
+          <t>TC-FORM-014</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 16: Form field state validation 16</t>
+          <t>Form interaction scenario 14: Form field state validation 14</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-017</t>
+          <t>TC-FORM-015</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 17: Form field state validation 17</t>
+          <t>Form interaction scenario 15: Form field state validation 15</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-018</t>
+          <t>TC-FORM-016</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 18: Form field state validation 18</t>
+          <t>Form interaction scenario 16: Form field state validation 16</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-019</t>
+          <t>TC-FORM-017</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 19: Form field state validation 19</t>
+          <t>Form interaction scenario 17: Form field state validation 17</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-020</t>
+          <t>TC-FORM-018</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 20: Form field state validation 20</t>
+          <t>Form interaction scenario 18: Form field state validation 18</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-021</t>
+          <t>TC-FORM-019</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 21: Form field state validation 21</t>
+          <t>Form interaction scenario 19: Form field state validation 19</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-022</t>
+          <t>TC-FORM-020</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 22: Form field state validation 22</t>
+          <t>Form interaction scenario 20: Form field state validation 20</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-023</t>
+          <t>TC-FORM-021</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 23: Form field state validation 23</t>
+          <t>Form interaction scenario 21: Form field state validation 21</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-024</t>
+          <t>TC-FORM-022</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 24: Form field state validation 24</t>
+          <t>Form interaction scenario 22: Form field state validation 22</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-025</t>
+          <t>TC-FORM-023</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 25: Form field state validation 25</t>
+          <t>Form interaction scenario 23: Form field state validation 23</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-026</t>
+          <t>TC-FORM-024</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 26: Form field state validation 26</t>
+          <t>Form interaction scenario 24: Form field state validation 24</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-027</t>
+          <t>TC-FORM-025</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 27: Form field state validation 27</t>
+          <t>Form interaction scenario 25: Form field state validation 25</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-028</t>
+          <t>TC-FORM-026</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 28: Form field state validation 28</t>
+          <t>Form interaction scenario 26: Form field state validation 26</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-029</t>
+          <t>TC-FORM-027</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 29: Form field state validation 29</t>
+          <t>Form interaction scenario 27: Form field state validation 27</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-030</t>
+          <t>TC-FORM-028</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 30: Form field state validation 30</t>
+          <t>Form interaction scenario 28: Form field state validation 28</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-031</t>
+          <t>TC-FORM-029</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 31: Form field state validation 31</t>
+          <t>Form interaction scenario 29: Form field state validation 29</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-032</t>
+          <t>TC-FORM-030</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 32: Form field state validation 32</t>
+          <t>Form interaction scenario 30: Form field state validation 30</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-033</t>
+          <t>TC-FORM-031</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 33: Form field state validation 33</t>
+          <t>Form interaction scenario 31: Form field state validation 31</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -6622,7 +6622,7 @@
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-034</t>
+          <t>TC-FORM-032</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 34: Form field state validation 34</t>
+          <t>Form interaction scenario 32: Form field state validation 32</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-035</t>
+          <t>TC-FORM-033</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 35: Form field state validation 35</t>
+          <t>Form interaction scenario 33: Form field state validation 33</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-036</t>
+          <t>TC-FORM-034</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 36: Form field state validation 36</t>
+          <t>Form interaction scenario 34: Form field state validation 34</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-037</t>
+          <t>TC-FORM-035</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 37: Form field state validation 37</t>
+          <t>Form interaction scenario 35: Form field state validation 35</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-038</t>
+          <t>TC-FORM-036</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 38: Form field state validation 38</t>
+          <t>Form interaction scenario 36: Form field state validation 36</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-039</t>
+          <t>TC-FORM-037</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 39: Form field state validation 39</t>
+          <t>Form interaction scenario 37: Form field state validation 37</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TC-FORM-040</t>
+          <t>TC-FORM-038</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Form interaction scenario 40: Form field state validation 40</t>
+          <t>Form interaction scenario 38: Form field state validation 38</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -6846,22 +6846,22 @@
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-001</t>
+          <t>TC-FORM-039</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 1 on clinical record</t>
+          <t>Form interaction scenario 39: Form field state validation 39</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
@@ -6878,22 +6878,22 @@
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-002</t>
+          <t>TC-FORM-040</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 2 on clinical record</t>
+          <t>Form interaction scenario 40: Form field state validation 40</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -6910,7 +6910,7 @@
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-003</t>
+          <t>TC-CRUD-001</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 3 on clinical record</t>
+          <t>Create operation scenario 1 on clinical record</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -6942,7 +6942,7 @@
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-004</t>
+          <t>TC-CRUD-002</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 4 on clinical record</t>
+          <t>Read operation scenario 2 on clinical record</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
@@ -6974,7 +6974,7 @@
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-005</t>
+          <t>TC-CRUD-003</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 5 on clinical record</t>
+          <t>Update operation scenario 3 on clinical record</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -7006,7 +7006,7 @@
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-006</t>
+          <t>TC-CRUD-004</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 6 on clinical record</t>
+          <t>Delete operation scenario 4 on clinical record</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-007</t>
+          <t>TC-CRUD-005</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 7 on clinical record</t>
+          <t>Create operation scenario 5 on clinical record</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -7070,7 +7070,7 @@
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-008</t>
+          <t>TC-CRUD-006</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 8 on clinical record</t>
+          <t>Read operation scenario 6 on clinical record</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
@@ -7102,7 +7102,7 @@
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-009</t>
+          <t>TC-CRUD-007</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 9 on clinical record</t>
+          <t>Update operation scenario 7 on clinical record</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -7134,7 +7134,7 @@
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-010</t>
+          <t>TC-CRUD-008</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 10 on clinical record</t>
+          <t>Delete operation scenario 8 on clinical record</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
     <row r="210" ht="20" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-011</t>
+          <t>TC-CRUD-009</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 11 on clinical record</t>
+          <t>Create operation scenario 9 on clinical record</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-012</t>
+          <t>TC-CRUD-010</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 12 on clinical record</t>
+          <t>Read operation scenario 10 on clinical record</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
@@ -7230,7 +7230,7 @@
     <row r="212" ht="20" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-013</t>
+          <t>TC-CRUD-011</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 13 on clinical record</t>
+          <t>Update operation scenario 11 on clinical record</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
@@ -7262,7 +7262,7 @@
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-014</t>
+          <t>TC-CRUD-012</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 14 on clinical record</t>
+          <t>Delete operation scenario 12 on clinical record</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -7294,7 +7294,7 @@
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-015</t>
+          <t>TC-CRUD-013</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 15 on clinical record</t>
+          <t>Create operation scenario 13 on clinical record</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -7326,7 +7326,7 @@
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-016</t>
+          <t>TC-CRUD-014</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 16 on clinical record</t>
+          <t>Read operation scenario 14 on clinical record</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
@@ -7358,7 +7358,7 @@
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-017</t>
+          <t>TC-CRUD-015</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 17 on clinical record</t>
+          <t>Update operation scenario 15 on clinical record</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-018</t>
+          <t>TC-CRUD-016</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 18 on clinical record</t>
+          <t>Delete operation scenario 16 on clinical record</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -7422,7 +7422,7 @@
     <row r="218" ht="20" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-019</t>
+          <t>TC-CRUD-017</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 19 on clinical record</t>
+          <t>Create operation scenario 17 on clinical record</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="219" ht="20" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-020</t>
+          <t>TC-CRUD-018</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 20 on clinical record</t>
+          <t>Read operation scenario 18 on clinical record</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
@@ -7486,7 +7486,7 @@
     <row r="220" ht="20" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-021</t>
+          <t>TC-CRUD-019</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 21 on clinical record</t>
+          <t>Update operation scenario 19 on clinical record</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
@@ -7518,7 +7518,7 @@
     <row r="221" ht="20" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-022</t>
+          <t>TC-CRUD-020</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 22 on clinical record</t>
+          <t>Delete operation scenario 20 on clinical record</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="222" ht="20" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-023</t>
+          <t>TC-CRUD-021</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 23 on clinical record</t>
+          <t>Create operation scenario 21 on clinical record</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -7582,7 +7582,7 @@
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-024</t>
+          <t>TC-CRUD-022</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 24 on clinical record</t>
+          <t>Read operation scenario 22 on clinical record</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
@@ -7614,7 +7614,7 @@
     <row r="224" ht="20" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-025</t>
+          <t>TC-CRUD-023</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 25 on clinical record</t>
+          <t>Update operation scenario 23 on clinical record</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
@@ -7646,7 +7646,7 @@
     <row r="225" ht="20" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-026</t>
+          <t>TC-CRUD-024</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 26 on clinical record</t>
+          <t>Delete operation scenario 24 on clinical record</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
@@ -7678,7 +7678,7 @@
     <row r="226" ht="20" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-027</t>
+          <t>TC-CRUD-025</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 27 on clinical record</t>
+          <t>Create operation scenario 25 on clinical record</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
     <row r="227" ht="20" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-028</t>
+          <t>TC-CRUD-026</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 28 on clinical record</t>
+          <t>Read operation scenario 26 on clinical record</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-029</t>
+          <t>TC-CRUD-027</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 29 on clinical record</t>
+          <t>Update operation scenario 27 on clinical record</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -7774,7 +7774,7 @@
     <row r="229" ht="20" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-030</t>
+          <t>TC-CRUD-028</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 30 on clinical record</t>
+          <t>Delete operation scenario 28 on clinical record</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
@@ -7806,7 +7806,7 @@
     <row r="230" ht="20" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-031</t>
+          <t>TC-CRUD-029</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 31 on clinical record</t>
+          <t>Create operation scenario 29 on clinical record</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
@@ -7838,7 +7838,7 @@
     <row r="231" ht="20" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-032</t>
+          <t>TC-CRUD-030</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 32 on clinical record</t>
+          <t>Read operation scenario 30 on clinical record</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
@@ -7870,7 +7870,7 @@
     <row r="232" ht="20" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-033</t>
+          <t>TC-CRUD-031</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 33 on clinical record</t>
+          <t>Update operation scenario 31 on clinical record</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -7902,7 +7902,7 @@
     <row r="233" ht="20" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-034</t>
+          <t>TC-CRUD-032</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 34 on clinical record</t>
+          <t>Delete operation scenario 32 on clinical record</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="234" ht="20" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-035</t>
+          <t>TC-CRUD-033</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 35 on clinical record</t>
+          <t>Create operation scenario 33 on clinical record</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -7966,7 +7966,7 @@
     <row r="235" ht="20" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-036</t>
+          <t>TC-CRUD-034</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 36 on clinical record</t>
+          <t>Read operation scenario 34 on clinical record</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="236" ht="20" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-037</t>
+          <t>TC-CRUD-035</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Create operation scenario 37 on clinical record</t>
+          <t>Update operation scenario 35 on clinical record</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -8030,7 +8030,7 @@
     <row r="237" ht="20" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-038</t>
+          <t>TC-CRUD-036</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Read operation scenario 38 on clinical record</t>
+          <t>Delete operation scenario 36 on clinical record</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -8062,7 +8062,7 @@
     <row r="238" ht="20" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-039</t>
+          <t>TC-CRUD-037</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Update operation scenario 39 on clinical record</t>
+          <t>Create operation scenario 37 on clinical record</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
     <row r="239" ht="20" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>TC-CRUD-040</t>
+          <t>TC-CRUD-038</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Delete operation scenario 40 on clinical record</t>
+          <t>Read operation scenario 38 on clinical record</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
@@ -8126,17 +8126,17 @@
     <row r="240" ht="20" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-001</t>
+          <t>TC-CRUD-039</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>CRUD Operations</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 1: Search biomarker by exact name (Hemoglobin)</t>
+          <t>Update operation scenario 39 on clinical record</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -8158,17 +8158,17 @@
     <row r="241" ht="20" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-002</t>
+          <t>TC-CRUD-040</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>CRUD Operations</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 2: Search biomarker by partial string (chol)</t>
+          <t>Delete operation scenario 40 on clinical record</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-003</t>
+          <t>TC-SRCH-001</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 3: Search with no matching results</t>
+          <t>Search feature scenario 1: Search biomarker by exact name (Hemoglobin)</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="243" ht="20" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-004</t>
+          <t>TC-SRCH-002</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 4: Search query debounce handling</t>
+          <t>Search feature scenario 2: Search biomarker by partial string (chol)</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -8254,7 +8254,7 @@
     <row r="244" ht="20" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-005</t>
+          <t>TC-SRCH-003</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 5: Biomarker catalog search 5</t>
+          <t>Search feature scenario 3: Search with no matching results</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="245" ht="20" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-006</t>
+          <t>TC-SRCH-004</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 6: Biomarker catalog search 6</t>
+          <t>Search feature scenario 4: Search query debounce handling</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
     <row r="246" ht="20" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-007</t>
+          <t>TC-SRCH-005</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 7: Biomarker catalog search 7</t>
+          <t>Search feature scenario 5: Biomarker catalog search 5</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -8350,7 +8350,7 @@
     <row r="247" ht="20" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-008</t>
+          <t>TC-SRCH-006</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 8: Biomarker catalog search 8</t>
+          <t>Search feature scenario 6: Biomarker catalog search 6</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -8382,7 +8382,7 @@
     <row r="248" ht="20" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-009</t>
+          <t>TC-SRCH-007</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 9: Biomarker catalog search 9</t>
+          <t>Search feature scenario 7: Biomarker catalog search 7</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
     <row r="249" ht="20" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-010</t>
+          <t>TC-SRCH-008</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 10: Biomarker catalog search 10</t>
+          <t>Search feature scenario 8: Biomarker catalog search 8</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
     <row r="250" ht="20" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-011</t>
+          <t>TC-SRCH-009</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 11: Biomarker catalog search 11</t>
+          <t>Search feature scenario 9: Biomarker catalog search 9</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="251" ht="20" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-012</t>
+          <t>TC-SRCH-010</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 12: Biomarker catalog search 12</t>
+          <t>Search feature scenario 10: Biomarker catalog search 10</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
     <row r="252" ht="20" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-013</t>
+          <t>TC-SRCH-011</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 13: Biomarker catalog search 13</t>
+          <t>Search feature scenario 11: Biomarker catalog search 11</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
     <row r="253" ht="20" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-014</t>
+          <t>TC-SRCH-012</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 14: Biomarker catalog search 14</t>
+          <t>Search feature scenario 12: Biomarker catalog search 12</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
     <row r="254" ht="20" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-015</t>
+          <t>TC-SRCH-013</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 15: Biomarker catalog search 15</t>
+          <t>Search feature scenario 13: Biomarker catalog search 13</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="255" ht="20" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-016</t>
+          <t>TC-SRCH-014</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 16: Biomarker catalog search 16</t>
+          <t>Search feature scenario 14: Biomarker catalog search 14</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
     <row r="256" ht="20" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-017</t>
+          <t>TC-SRCH-015</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 17: Biomarker catalog search 17</t>
+          <t>Search feature scenario 15: Biomarker catalog search 15</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -8670,7 +8670,7 @@
     <row r="257" ht="20" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-018</t>
+          <t>TC-SRCH-016</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 18: Biomarker catalog search 18</t>
+          <t>Search feature scenario 16: Biomarker catalog search 16</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -8702,7 +8702,7 @@
     <row r="258" ht="20" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-019</t>
+          <t>TC-SRCH-017</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 19: Biomarker catalog search 19</t>
+          <t>Search feature scenario 17: Biomarker catalog search 17</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -8734,7 +8734,7 @@
     <row r="259" ht="20" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>TC-SRCH-020</t>
+          <t>TC-SRCH-018</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Search feature scenario 20: Biomarker catalog search 20</t>
+          <t>Search feature scenario 18: Biomarker catalog search 18</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -8766,17 +8766,17 @@
     <row r="260" ht="20" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-001</t>
+          <t>TC-SRCH-019</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 1: Filter by High/Abnormal status</t>
+          <t>Search feature scenario 19: Biomarker catalog search 19</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -8798,17 +8798,17 @@
     <row r="261" ht="20" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-002</t>
+          <t>TC-SRCH-020</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 2: Filter by Normal status</t>
+          <t>Search feature scenario 20: Biomarker catalog search 20</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
     <row r="262" ht="20" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-003</t>
+          <t>TC-FLTR-001</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 3: Filter by Organ System (Lipid / Renal / Hepatic)</t>
+          <t>Biomarker filter scenario 1: Filter by High/Abnormal status</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="263" ht="20" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-004</t>
+          <t>TC-FLTR-002</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 4: Reset all active filters</t>
+          <t>Biomarker filter scenario 2: Filter by Normal status</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="264" ht="20" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-005</t>
+          <t>TC-FLTR-003</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 5: Multi-criteria filter combination 5</t>
+          <t>Biomarker filter scenario 3: Filter by Organ System (Lipid / Renal / Hepatic)</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
     <row r="265" ht="20" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-006</t>
+          <t>TC-FLTR-004</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 6: Multi-criteria filter combination 6</t>
+          <t>Biomarker filter scenario 4: Reset all active filters</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
     <row r="266" ht="20" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-007</t>
+          <t>TC-FLTR-005</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 7: Multi-criteria filter combination 7</t>
+          <t>Biomarker filter scenario 5: Multi-criteria filter combination 5</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
     <row r="267" ht="20" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-008</t>
+          <t>TC-FLTR-006</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 8: Multi-criteria filter combination 8</t>
+          <t>Biomarker filter scenario 6: Multi-criteria filter combination 6</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="268" ht="20" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-009</t>
+          <t>TC-FLTR-007</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 9: Multi-criteria filter combination 9</t>
+          <t>Biomarker filter scenario 7: Multi-criteria filter combination 7</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="269" ht="20" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-010</t>
+          <t>TC-FLTR-008</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 10: Multi-criteria filter combination 10</t>
+          <t>Biomarker filter scenario 8: Multi-criteria filter combination 8</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
     <row r="270" ht="20" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-011</t>
+          <t>TC-FLTR-009</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 11: Multi-criteria filter combination 11</t>
+          <t>Biomarker filter scenario 9: Multi-criteria filter combination 9</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
     <row r="271" ht="20" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-012</t>
+          <t>TC-FLTR-010</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 12: Multi-criteria filter combination 12</t>
+          <t>Biomarker filter scenario 10: Multi-criteria filter combination 10</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -9150,7 +9150,7 @@
     <row r="272" ht="20" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-013</t>
+          <t>TC-FLTR-011</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 13: Multi-criteria filter combination 13</t>
+          <t>Biomarker filter scenario 11: Multi-criteria filter combination 11</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
     <row r="273" ht="20" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-014</t>
+          <t>TC-FLTR-012</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 14: Multi-criteria filter combination 14</t>
+          <t>Biomarker filter scenario 12: Multi-criteria filter combination 12</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
     <row r="274" ht="20" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-015</t>
+          <t>TC-FLTR-013</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 15: Multi-criteria filter combination 15</t>
+          <t>Biomarker filter scenario 13: Multi-criteria filter combination 13</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
     <row r="275" ht="20" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-016</t>
+          <t>TC-FLTR-014</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 16: Multi-criteria filter combination 16</t>
+          <t>Biomarker filter scenario 14: Multi-criteria filter combination 14</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
     <row r="276" ht="20" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-017</t>
+          <t>TC-FLTR-015</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 17: Multi-criteria filter combination 17</t>
+          <t>Biomarker filter scenario 15: Multi-criteria filter combination 15</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -9310,7 +9310,7 @@
     <row r="277" ht="20" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-018</t>
+          <t>TC-FLTR-016</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 18: Multi-criteria filter combination 18</t>
+          <t>Biomarker filter scenario 16: Multi-criteria filter combination 16</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -9342,7 +9342,7 @@
     <row r="278" ht="20" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-019</t>
+          <t>TC-FLTR-017</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 19: Multi-criteria filter combination 19</t>
+          <t>Biomarker filter scenario 17: Multi-criteria filter combination 17</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
     <row r="279" ht="20" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>TC-FLTR-020</t>
+          <t>TC-FLTR-018</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Biomarker filter scenario 20: Multi-criteria filter combination 20</t>
+          <t>Biomarker filter scenario 18: Multi-criteria filter combination 18</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -9406,22 +9406,22 @@
     <row r="280" ht="20" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-001</t>
+          <t>TC-FLTR-019</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 1: Negative biomarker value rejection</t>
+          <t>Biomarker filter scenario 19: Multi-criteria filter combination 19</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -9438,22 +9438,22 @@
     <row r="281" ht="20" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-002</t>
+          <t>TC-FLTR-020</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 2: Physiologically impossible value warning</t>
+          <t>Biomarker filter scenario 20: Multi-criteria filter combination 20</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -9470,7 +9470,7 @@
     <row r="282" ht="20" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-003</t>
+          <t>TC-INP-001</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 3: Special characters in patient name</t>
+          <t>Boundary input validation 1: Negative biomarker value rejection</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
     <row r="283" ht="20" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-004</t>
+          <t>TC-INP-002</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 4: Extreme numeric boundary test</t>
+          <t>Boundary input validation 2: Physiologically impossible value warning</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
     <row r="284" ht="20" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-005</t>
+          <t>TC-INP-003</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 5: Input boundary validation sequence 5</t>
+          <t>Boundary input validation 3: Special characters in patient name</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="285" ht="20" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-006</t>
+          <t>TC-INP-004</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 6: Input boundary validation sequence 6</t>
+          <t>Boundary input validation 4: Extreme numeric boundary test</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
     <row r="286" ht="20" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-007</t>
+          <t>TC-INP-005</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 7: Input boundary validation sequence 7</t>
+          <t>Boundary input validation 5: Input boundary validation sequence 5</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
     <row r="287" ht="20" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-008</t>
+          <t>TC-INP-006</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 8: Input boundary validation sequence 8</t>
+          <t>Boundary input validation 6: Input boundary validation sequence 6</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
     <row r="288" ht="20" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-009</t>
+          <t>TC-INP-007</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 9: Input boundary validation sequence 9</t>
+          <t>Boundary input validation 7: Input boundary validation sequence 7</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="289" ht="20" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-010</t>
+          <t>TC-INP-008</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 10: Input boundary validation sequence 10</t>
+          <t>Boundary input validation 8: Input boundary validation sequence 8</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
     <row r="290" ht="20" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-011</t>
+          <t>TC-INP-009</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 11: Input boundary validation sequence 11</t>
+          <t>Boundary input validation 9: Input boundary validation sequence 9</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
     <row r="291" ht="20" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-012</t>
+          <t>TC-INP-010</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 12: Input boundary validation sequence 12</t>
+          <t>Boundary input validation 10: Input boundary validation sequence 10</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
     <row r="292" ht="20" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-013</t>
+          <t>TC-INP-011</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 13: Input boundary validation sequence 13</t>
+          <t>Boundary input validation 11: Input boundary validation sequence 11</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
     <row r="293" ht="20" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-014</t>
+          <t>TC-INP-012</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 14: Input boundary validation sequence 14</t>
+          <t>Boundary input validation 12: Input boundary validation sequence 12</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
     <row r="294" ht="20" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-015</t>
+          <t>TC-INP-013</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 15: Input boundary validation sequence 15</t>
+          <t>Boundary input validation 13: Input boundary validation sequence 13</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
     <row r="295" ht="20" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-016</t>
+          <t>TC-INP-014</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 16: Input boundary validation sequence 16</t>
+          <t>Boundary input validation 14: Input boundary validation sequence 14</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
     <row r="296" ht="20" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-017</t>
+          <t>TC-INP-015</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 17: Input boundary validation sequence 17</t>
+          <t>Boundary input validation 15: Input boundary validation sequence 15</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
     <row r="297" ht="20" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-018</t>
+          <t>TC-INP-016</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 18: Input boundary validation sequence 18</t>
+          <t>Boundary input validation 16: Input boundary validation sequence 16</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
     <row r="298" ht="20" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-019</t>
+          <t>TC-INP-017</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 19: Input boundary validation sequence 19</t>
+          <t>Boundary input validation 17: Input boundary validation sequence 17</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -10014,7 +10014,7 @@
     <row r="299" ht="20" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-020</t>
+          <t>TC-INP-018</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 20: Input boundary validation sequence 20</t>
+          <t>Boundary input validation 18: Input boundary validation sequence 18</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -10046,7 +10046,7 @@
     <row r="300" ht="20" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-021</t>
+          <t>TC-INP-019</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 21: Input boundary validation sequence 21</t>
+          <t>Boundary input validation 19: Input boundary validation sequence 19</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
     <row r="301" ht="20" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-022</t>
+          <t>TC-INP-020</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 22: Input boundary validation sequence 22</t>
+          <t>Boundary input validation 20: Input boundary validation sequence 20</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="302" ht="20" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-023</t>
+          <t>TC-INP-021</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 23: Input boundary validation sequence 23</t>
+          <t>Boundary input validation 21: Input boundary validation sequence 21</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
     <row r="303" ht="20" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-024</t>
+          <t>TC-INP-022</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 24: Input boundary validation sequence 24</t>
+          <t>Boundary input validation 22: Input boundary validation sequence 22</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
     <row r="304" ht="20" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-025</t>
+          <t>TC-INP-023</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 25: Input boundary validation sequence 25</t>
+          <t>Boundary input validation 23: Input boundary validation sequence 23</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -10206,7 +10206,7 @@
     <row r="305" ht="20" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-026</t>
+          <t>TC-INP-024</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 26: Input boundary validation sequence 26</t>
+          <t>Boundary input validation 24: Input boundary validation sequence 24</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="306" ht="20" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-027</t>
+          <t>TC-INP-025</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 27: Input boundary validation sequence 27</t>
+          <t>Boundary input validation 25: Input boundary validation sequence 25</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
     <row r="307" ht="20" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-028</t>
+          <t>TC-INP-026</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 28: Input boundary validation sequence 28</t>
+          <t>Boundary input validation 26: Input boundary validation sequence 26</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -10302,7 +10302,7 @@
     <row r="308" ht="20" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-029</t>
+          <t>TC-INP-027</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 29: Input boundary validation sequence 29</t>
+          <t>Boundary input validation 27: Input boundary validation sequence 27</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row r="309" ht="20" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-030</t>
+          <t>TC-INP-028</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 30: Input boundary validation sequence 30</t>
+          <t>Boundary input validation 28: Input boundary validation sequence 28</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -10366,7 +10366,7 @@
     <row r="310" ht="20" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-031</t>
+          <t>TC-INP-029</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 31: Input boundary validation sequence 31</t>
+          <t>Boundary input validation 29: Input boundary validation sequence 29</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -10398,7 +10398,7 @@
     <row r="311" ht="20" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-032</t>
+          <t>TC-INP-030</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 32: Input boundary validation sequence 32</t>
+          <t>Boundary input validation 30: Input boundary validation sequence 30</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -10430,7 +10430,7 @@
     <row r="312" ht="20" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-033</t>
+          <t>TC-INP-031</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 33: Input boundary validation sequence 33</t>
+          <t>Boundary input validation 31: Input boundary validation sequence 31</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -10462,7 +10462,7 @@
     <row r="313" ht="20" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-034</t>
+          <t>TC-INP-032</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 34: Input boundary validation sequence 34</t>
+          <t>Boundary input validation 32: Input boundary validation sequence 32</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="314" ht="20" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-035</t>
+          <t>TC-INP-033</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 35: Input boundary validation sequence 35</t>
+          <t>Boundary input validation 33: Input boundary validation sequence 33</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
     <row r="315" ht="20" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-036</t>
+          <t>TC-INP-034</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 36: Input boundary validation sequence 36</t>
+          <t>Boundary input validation 34: Input boundary validation sequence 34</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -10558,7 +10558,7 @@
     <row r="316" ht="20" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-037</t>
+          <t>TC-INP-035</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 37: Input boundary validation sequence 37</t>
+          <t>Boundary input validation 35: Input boundary validation sequence 35</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
     <row r="317" ht="20" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-038</t>
+          <t>TC-INP-036</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 38: Input boundary validation sequence 38</t>
+          <t>Boundary input validation 36: Input boundary validation sequence 36</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
     <row r="318" ht="20" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-039</t>
+          <t>TC-INP-037</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 39: Input boundary validation sequence 39</t>
+          <t>Boundary input validation 37: Input boundary validation sequence 37</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="319" ht="20" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>TC-INP-040</t>
+          <t>TC-INP-038</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Boundary input validation 40: Input boundary validation sequence 40</t>
+          <t>Boundary input validation 38: Input boundary validation sequence 38</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -10686,17 +10686,17 @@
     <row r="320" ht="20" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-001</t>
+          <t>TC-INP-039</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 1: Network timeout during report analysis</t>
+          <t>Boundary input validation 39: Input boundary validation sequence 39</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -10718,17 +10718,17 @@
     <row r="321" ht="20" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-002</t>
+          <t>TC-INP-040</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 2: Backend HTTP 500 error toast</t>
+          <t>Boundary input validation 40: Input boundary validation sequence 40</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
     <row r="322" ht="20" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-004</t>
+          <t>TC-ERR-001</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 4: Retry button functionality on failure banner</t>
+          <t>Error resilience scenario 1: Network timeout during report analysis</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
     <row r="323" ht="20" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-005</t>
+          <t>TC-ERR-002</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 5: System exception handling scenario 5</t>
+          <t>Error resilience scenario 2: Backend HTTP 500 error toast</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
     <row r="324" ht="20" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-006</t>
+          <t>TC-ERR-003</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 6: System exception handling scenario 6</t>
+          <t>Error resilience scenario 3: Corrupt PDF document upload error</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
     <row r="325" ht="20" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-007</t>
+          <t>TC-ERR-004</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 7: System exception handling scenario 7</t>
+          <t>Error resilience scenario 4: Retry button functionality on failure banner</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
     <row r="326" ht="20" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-008</t>
+          <t>TC-ERR-005</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 8: System exception handling scenario 8</t>
+          <t>Error resilience scenario 5: System exception handling scenario 5</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="327" ht="20" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-009</t>
+          <t>TC-ERR-006</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 9: System exception handling scenario 9</t>
+          <t>Error resilience scenario 6: System exception handling scenario 6</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
     <row r="328" ht="20" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-010</t>
+          <t>TC-ERR-007</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 10: System exception handling scenario 10</t>
+          <t>Error resilience scenario 7: System exception handling scenario 7</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -10974,7 +10974,7 @@
     <row r="329" ht="20" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-011</t>
+          <t>TC-ERR-008</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 11: System exception handling scenario 11</t>
+          <t>Error resilience scenario 8: System exception handling scenario 8</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
@@ -11006,7 +11006,7 @@
     <row r="330" ht="20" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-012</t>
+          <t>TC-ERR-009</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 12: System exception handling scenario 12</t>
+          <t>Error resilience scenario 9: System exception handling scenario 9</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="331" ht="20" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-013</t>
+          <t>TC-ERR-010</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 13: System exception handling scenario 13</t>
+          <t>Error resilience scenario 10: System exception handling scenario 10</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
     <row r="332" ht="20" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-014</t>
+          <t>TC-ERR-011</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 14: System exception handling scenario 14</t>
+          <t>Error resilience scenario 11: System exception handling scenario 11</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
     <row r="333" ht="20" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-015</t>
+          <t>TC-ERR-012</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 15: System exception handling scenario 15</t>
+          <t>Error resilience scenario 12: System exception handling scenario 12</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
     <row r="334" ht="20" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-016</t>
+          <t>TC-ERR-013</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 16: System exception handling scenario 16</t>
+          <t>Error resilience scenario 13: System exception handling scenario 13</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
     <row r="335" ht="20" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-017</t>
+          <t>TC-ERR-014</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 17: System exception handling scenario 17</t>
+          <t>Error resilience scenario 14: System exception handling scenario 14</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="336" ht="20" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-018</t>
+          <t>TC-ERR-015</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 18: System exception handling scenario 18</t>
+          <t>Error resilience scenario 15: System exception handling scenario 15</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -11230,7 +11230,7 @@
     <row r="337" ht="20" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-019</t>
+          <t>TC-ERR-016</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 19: System exception handling scenario 19</t>
+          <t>Error resilience scenario 16: System exception handling scenario 16</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
@@ -11262,7 +11262,7 @@
     <row r="338" ht="20" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>TC-ERR-020</t>
+          <t>TC-ERR-017</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Error resilience scenario 20: System exception handling scenario 20</t>
+          <t>Error resilience scenario 17: System exception handling scenario 17</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -11294,22 +11294,22 @@
     <row r="339" ht="20" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-001</t>
+          <t>TC-ERR-018</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 1: App killed and restored state retention</t>
+          <t>Error resilience scenario 18: System exception handling scenario 18</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E339" s="3" t="inlineStr">
@@ -11326,22 +11326,22 @@
     <row r="340" ht="20" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-002</t>
+          <t>TC-ERR-019</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 2: JWT session expiration refresh</t>
+          <t>Error resilience scenario 19: System exception handling scenario 19</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
@@ -11358,22 +11358,22 @@
     <row r="341" ht="20" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-003</t>
+          <t>TC-ERR-020</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 3: Explicit logout token clearance</t>
+          <t>Error resilience scenario 20: System exception handling scenario 20</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E341" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
     <row r="342" ht="20" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-004</t>
+          <t>TC-SESS-001</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 4: Concurrent session handling</t>
+          <t>Session lifecycle scenario 1: App killed and restored state retention</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
     <row r="343" ht="20" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-005</t>
+          <t>TC-SESS-002</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 5: Session persistence verification 5</t>
+          <t>Session lifecycle scenario 2: JWT session expiration refresh</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E343" s="3" t="inlineStr">
@@ -11454,7 +11454,7 @@
     <row r="344" ht="20" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-006</t>
+          <t>TC-SESS-003</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 6: Session persistence verification 6</t>
+          <t>Session lifecycle scenario 3: Explicit logout token clearance</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
     <row r="345" ht="20" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-007</t>
+          <t>TC-SESS-004</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 7: Session persistence verification 7</t>
+          <t>Session lifecycle scenario 4: Concurrent session handling</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
     <row r="346" ht="20" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-008</t>
+          <t>TC-SESS-005</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 8: Session persistence verification 8</t>
+          <t>Session lifecycle scenario 5: Session persistence verification 5</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -11550,7 +11550,7 @@
     <row r="347" ht="20" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-009</t>
+          <t>TC-SESS-006</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 9: Session persistence verification 9</t>
+          <t>Session lifecycle scenario 6: Session persistence verification 6</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="348" ht="20" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-010</t>
+          <t>TC-SESS-007</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 10: Session persistence verification 10</t>
+          <t>Session lifecycle scenario 7: Session persistence verification 7</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="349" ht="20" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-011</t>
+          <t>TC-SESS-008</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 11: Session persistence verification 11</t>
+          <t>Session lifecycle scenario 8: Session persistence verification 8</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
     <row r="350" ht="20" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-012</t>
+          <t>TC-SESS-009</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 12: Session persistence verification 12</t>
+          <t>Session lifecycle scenario 9: Session persistence verification 9</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -11678,7 +11678,7 @@
     <row r="351" ht="20" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-013</t>
+          <t>TC-SESS-010</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 13: Session persistence verification 13</t>
+          <t>Session lifecycle scenario 10: Session persistence verification 10</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="352" ht="20" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-014</t>
+          <t>TC-SESS-011</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 14: Session persistence verification 14</t>
+          <t>Session lifecycle scenario 11: Session persistence verification 11</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="353" ht="20" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-015</t>
+          <t>TC-SESS-012</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 15: Session persistence verification 15</t>
+          <t>Session lifecycle scenario 12: Session persistence verification 12</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -11774,7 +11774,7 @@
     <row r="354" ht="20" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-016</t>
+          <t>TC-SESS-013</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 16: Session persistence verification 16</t>
+          <t>Session lifecycle scenario 13: Session persistence verification 13</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
     <row r="355" ht="20" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-017</t>
+          <t>TC-SESS-014</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 17: Session persistence verification 17</t>
+          <t>Session lifecycle scenario 14: Session persistence verification 14</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -11838,7 +11838,7 @@
     <row r="356" ht="20" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-018</t>
+          <t>TC-SESS-015</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 18: Session persistence verification 18</t>
+          <t>Session lifecycle scenario 15: Session persistence verification 15</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
     <row r="357" ht="20" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-019</t>
+          <t>TC-SESS-016</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 19: Session persistence verification 19</t>
+          <t>Session lifecycle scenario 16: Session persistence verification 16</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
     <row r="358" ht="20" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>TC-SESS-020</t>
+          <t>TC-SESS-017</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Session lifecycle scenario 20: Session persistence verification 20</t>
+          <t>Session lifecycle scenario 17: Session persistence verification 17</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -11934,17 +11934,17 @@
     <row r="359" ht="20" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-001</t>
+          <t>TC-SESS-018</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 1: Critical biomarker alert toast</t>
+          <t>Session lifecycle scenario 18: Session persistence verification 18</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -11966,17 +11966,17 @@
     <row r="360" ht="20" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-002</t>
+          <t>TC-SESS-019</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 2: Report processing complete banner</t>
+          <t>Session lifecycle scenario 19: Session persistence verification 19</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -11998,17 +11998,17 @@
     <row r="361" ht="20" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-003</t>
+          <t>TC-SESS-020</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 3: In-app badge counter update</t>
+          <t>Session lifecycle scenario 20: Session persistence verification 20</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
     <row r="362" ht="20" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-004</t>
+          <t>TC-NOTIF-001</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 4: Notification permission prompt handling</t>
+          <t>Clinical alert notification 1: Critical biomarker alert toast</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="363" ht="20" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-005</t>
+          <t>TC-NOTIF-002</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 5: Notification channel scenario 5</t>
+          <t>Clinical alert notification 2: Report processing complete banner</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="364" ht="20" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-006</t>
+          <t>TC-NOTIF-003</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 6: Notification channel scenario 6</t>
+          <t>Clinical alert notification 3: In-app badge counter update</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
     <row r="365" ht="20" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-007</t>
+          <t>TC-NOTIF-004</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 7: Notification channel scenario 7</t>
+          <t>Clinical alert notification 4: Notification permission prompt handling</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
     <row r="366" ht="20" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-008</t>
+          <t>TC-NOTIF-005</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 8: Notification channel scenario 8</t>
+          <t>Clinical alert notification 5: Notification channel scenario 5</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
     <row r="367" ht="20" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-009</t>
+          <t>TC-NOTIF-006</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 9: Notification channel scenario 9</t>
+          <t>Clinical alert notification 6: Notification channel scenario 6</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
     <row r="368" ht="20" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-010</t>
+          <t>TC-NOTIF-007</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 10: Notification channel scenario 10</t>
+          <t>Clinical alert notification 7: Notification channel scenario 7</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="369" ht="20" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-011</t>
+          <t>TC-NOTIF-008</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 11: Notification channel scenario 11</t>
+          <t>Clinical alert notification 8: Notification channel scenario 8</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="370" ht="20" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-012</t>
+          <t>TC-NOTIF-009</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 12: Notification channel scenario 12</t>
+          <t>Clinical alert notification 9: Notification channel scenario 9</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -12318,7 +12318,7 @@
     <row r="371" ht="20" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-013</t>
+          <t>TC-NOTIF-010</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 13: Notification channel scenario 13</t>
+          <t>Clinical alert notification 10: Notification channel scenario 10</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -12350,7 +12350,7 @@
     <row r="372" ht="20" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-014</t>
+          <t>TC-NOTIF-011</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 14: Notification channel scenario 14</t>
+          <t>Clinical alert notification 11: Notification channel scenario 11</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="373" ht="20" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-015</t>
+          <t>TC-NOTIF-012</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 15: Notification channel scenario 15</t>
+          <t>Clinical alert notification 12: Notification channel scenario 12</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="374" ht="20" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-016</t>
+          <t>TC-NOTIF-013</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 16: Notification channel scenario 16</t>
+          <t>Clinical alert notification 13: Notification channel scenario 13</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
     <row r="375" ht="20" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-017</t>
+          <t>TC-NOTIF-014</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 17: Notification channel scenario 17</t>
+          <t>Clinical alert notification 14: Notification channel scenario 14</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -12478,7 +12478,7 @@
     <row r="376" ht="20" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-018</t>
+          <t>TC-NOTIF-015</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 18: Notification channel scenario 18</t>
+          <t>Clinical alert notification 15: Notification channel scenario 15</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
     <row r="377" ht="20" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-019</t>
+          <t>TC-NOTIF-016</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 19: Notification channel scenario 19</t>
+          <t>Clinical alert notification 16: Notification channel scenario 16</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
     <row r="378" ht="20" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>TC-NOTIF-020</t>
+          <t>TC-NOTIF-017</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Clinical alert notification 20: Notification channel scenario 20</t>
+          <t>Clinical alert notification 17: Notification channel scenario 17</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -12574,22 +12574,22 @@
     <row r="379" ht="20" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-001</t>
+          <t>TC-NOTIF-018</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 1: Pick standard lab report PDF from storage</t>
+          <t>Clinical alert notification 18: Notification channel scenario 18</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
@@ -12606,22 +12606,22 @@
     <row r="380" ht="20" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-002</t>
+          <t>TC-NOTIF-019</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 2: Pick report image (JPEG/PNG) from gallery</t>
+          <t>Clinical alert notification 19: Notification channel scenario 19</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
@@ -12638,22 +12638,22 @@
     <row r="381" ht="20" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-003</t>
+          <t>TC-NOTIF-020</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 3: Capture photo using device camera</t>
+          <t>Clinical alert notification 20: Notification channel scenario 20</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr">
@@ -12670,7 +12670,7 @@
     <row r="382" ht="20" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-005</t>
+          <t>TC-UPL-001</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 5: File format and MIME upload scenario 5</t>
+          <t>Mobile document upload scenario 1: Pick standard lab report PDF from storage</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
@@ -12702,7 +12702,7 @@
     <row r="383" ht="20" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-006</t>
+          <t>TC-UPL-002</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 6: File format and MIME upload scenario 6</t>
+          <t>Mobile document upload scenario 2: Pick report image (JPEG/PNG) from gallery</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="384" ht="20" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-007</t>
+          <t>TC-UPL-003</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 7: File format and MIME upload scenario 7</t>
+          <t>Mobile document upload scenario 3: Capture photo using device camera</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
@@ -12766,7 +12766,7 @@
     <row r="385" ht="20" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-008</t>
+          <t>TC-UPL-004</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -12776,12 +12776,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 8: File format and MIME upload scenario 8</t>
+          <t>Mobile document upload scenario 4: Oversized 25MB file upload rejection</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
     <row r="386" ht="20" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-009</t>
+          <t>TC-UPL-005</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 9: File format and MIME upload scenario 9</t>
+          <t>Mobile document upload scenario 5: File format and MIME upload scenario 5</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
     <row r="387" ht="20" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-010</t>
+          <t>TC-UPL-006</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 10: File format and MIME upload scenario 10</t>
+          <t>Mobile document upload scenario 6: File format and MIME upload scenario 6</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
     <row r="388" ht="20" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-011</t>
+          <t>TC-UPL-007</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 11: File format and MIME upload scenario 11</t>
+          <t>Mobile document upload scenario 7: File format and MIME upload scenario 7</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="389" ht="20" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-012</t>
+          <t>TC-UPL-008</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 12: File format and MIME upload scenario 12</t>
+          <t>Mobile document upload scenario 8: File format and MIME upload scenario 8</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="390" ht="20" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-013</t>
+          <t>TC-UPL-009</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 13: File format and MIME upload scenario 13</t>
+          <t>Mobile document upload scenario 9: File format and MIME upload scenario 9</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
     <row r="391" ht="20" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-014</t>
+          <t>TC-UPL-010</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 14: File format and MIME upload scenario 14</t>
+          <t>Mobile document upload scenario 10: File format and MIME upload scenario 10</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -12990,7 +12990,7 @@
     <row r="392" ht="20" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-015</t>
+          <t>TC-UPL-011</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 15: File format and MIME upload scenario 15</t>
+          <t>Mobile document upload scenario 11: File format and MIME upload scenario 11</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="393" ht="20" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-016</t>
+          <t>TC-UPL-012</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 16: File format and MIME upload scenario 16</t>
+          <t>Mobile document upload scenario 12: File format and MIME upload scenario 12</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="394" ht="20" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-017</t>
+          <t>TC-UPL-013</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 17: File format and MIME upload scenario 17</t>
+          <t>Mobile document upload scenario 13: File format and MIME upload scenario 13</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -13086,7 +13086,7 @@
     <row r="395" ht="20" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-018</t>
+          <t>TC-UPL-014</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 18: File format and MIME upload scenario 18</t>
+          <t>Mobile document upload scenario 14: File format and MIME upload scenario 14</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
@@ -13118,7 +13118,7 @@
     <row r="396" ht="20" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-019</t>
+          <t>TC-UPL-015</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 19: File format and MIME upload scenario 19</t>
+          <t>Mobile document upload scenario 15: File format and MIME upload scenario 15</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="397" ht="20" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>TC-UPL-020</t>
+          <t>TC-UPL-016</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>Mobile document upload scenario 20: File format and MIME upload scenario 20</t>
+          <t>Mobile document upload scenario 16: File format and MIME upload scenario 16</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -13182,17 +13182,17 @@
     <row r="398" ht="20" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-001</t>
+          <t>TC-UPL-017</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 1: Airplane mode report analysis fallback</t>
+          <t>Mobile document upload scenario 17: File format and MIME upload scenario 17</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -13214,17 +13214,17 @@
     <row r="399" ht="20" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-002</t>
+          <t>TC-UPL-018</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 2: Offline cached biomarker range viewing</t>
+          <t>Mobile document upload scenario 18: File format and MIME upload scenario 18</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
@@ -13246,17 +13246,17 @@
     <row r="400" ht="20" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-003</t>
+          <t>TC-UPL-019</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 3: Pending report sync queue on reconnect</t>
+          <t>Mobile document upload scenario 19: File format and MIME upload scenario 19</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
@@ -13278,17 +13278,17 @@
     <row r="401" ht="20" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-004</t>
+          <t>TC-UPL-020</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 4: Offline disclaimer banner display</t>
+          <t>Mobile document upload scenario 20: File format and MIME upload scenario 20</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
@@ -13310,7 +13310,7 @@
     <row r="402" ht="20" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-005</t>
+          <t>TC-OFF-001</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 5: Offline network resilience scenario 5</t>
+          <t>Offline mode scenario 1: Airplane mode report analysis fallback</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
     <row r="403" ht="20" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-006</t>
+          <t>TC-OFF-002</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 6: Offline network resilience scenario 6</t>
+          <t>Offline mode scenario 2: Offline cached biomarker range viewing</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="404" ht="20" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-007</t>
+          <t>TC-OFF-003</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 7: Offline network resilience scenario 7</t>
+          <t>Offline mode scenario 3: Pending report sync queue on reconnect</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
@@ -13406,7 +13406,7 @@
     <row r="405" ht="20" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-008</t>
+          <t>TC-OFF-004</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 8: Offline network resilience scenario 8</t>
+          <t>Offline mode scenario 4: Offline disclaimer banner display</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
@@ -13438,7 +13438,7 @@
     <row r="406" ht="20" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-009</t>
+          <t>TC-OFF-005</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 9: Offline network resilience scenario 9</t>
+          <t>Offline mode scenario 5: Offline network resilience scenario 5</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
@@ -13470,7 +13470,7 @@
     <row r="407" ht="20" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>TC-OFF-010</t>
+          <t>TC-OFF-006</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>Offline mode scenario 10: Offline network resilience scenario 10</t>
+          <t>Offline mode scenario 6: Offline network resilience scenario 6</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
@@ -13502,22 +13502,22 @@
     <row r="408" ht="20" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-001</t>
+          <t>TC-OFF-007</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Offline Handling</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 1: TalkBack screen reader contentDescription on buttons</t>
+          <t>Offline mode scenario 7: Offline network resilience scenario 7</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
@@ -13534,22 +13534,22 @@
     <row r="409" ht="20" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-002</t>
+          <t>TC-OFF-008</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Offline Handling</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 2: Minimum touch target size (48x48 dp)</t>
+          <t>Offline mode scenario 8: Offline network resilience scenario 8</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
@@ -13566,22 +13566,22 @@
     <row r="410" ht="20" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-003</t>
+          <t>TC-OFF-009</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Offline Handling</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 3: High contrast text ratio (WCAG AA)</t>
+          <t>Offline mode scenario 9: Offline network resilience scenario 9</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
@@ -13598,22 +13598,22 @@
     <row r="411" ht="20" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-004</t>
+          <t>TC-OFF-010</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Offline Handling</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 4: Dynamic font scaling support (large text)</t>
+          <t>Offline mode scenario 10: Offline network resilience scenario 10</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
@@ -13630,7 +13630,7 @@
     <row r="412" ht="20" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-005</t>
+          <t>TC-A11Y-001</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 5: Accessibility compliance check 5</t>
+          <t>Mobile accessibility check 1: TalkBack screen reader contentDescription on buttons</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -13662,7 +13662,7 @@
     <row r="413" ht="20" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-006</t>
+          <t>TC-A11Y-002</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 6: Accessibility compliance check 6</t>
+          <t>Mobile accessibility check 2: Minimum touch target size (48x48 dp)</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="414" ht="20" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-007</t>
+          <t>TC-A11Y-003</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 7: Accessibility compliance check 7</t>
+          <t>Mobile accessibility check 3: High contrast text ratio (WCAG AA)</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
     <row r="415" ht="20" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-008</t>
+          <t>TC-A11Y-004</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 8: Accessibility compliance check 8</t>
+          <t>Mobile accessibility check 4: Dynamic font scaling support (large text)</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
@@ -13758,7 +13758,7 @@
     <row r="416" ht="20" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-009</t>
+          <t>TC-A11Y-005</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 9: Accessibility compliance check 9</t>
+          <t>Mobile accessibility check 5: Accessibility compliance check 5</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
@@ -13790,7 +13790,7 @@
     <row r="417" ht="20" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-010</t>
+          <t>TC-A11Y-006</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 10: Accessibility compliance check 10</t>
+          <t>Mobile accessibility check 6: Accessibility compliance check 6</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
     <row r="418" ht="20" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-011</t>
+          <t>TC-A11Y-007</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 11: Accessibility compliance check 11</t>
+          <t>Mobile accessibility check 7: Accessibility compliance check 7</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="419" ht="20" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-012</t>
+          <t>TC-A11Y-008</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 12: Accessibility compliance check 12</t>
+          <t>Mobile accessibility check 8: Accessibility compliance check 8</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
     <row r="420" ht="20" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-013</t>
+          <t>TC-A11Y-009</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 13: Accessibility compliance check 13</t>
+          <t>Mobile accessibility check 9: Accessibility compliance check 9</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -13918,7 +13918,7 @@
     <row r="421" ht="20" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-014</t>
+          <t>TC-A11Y-010</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 14: Accessibility compliance check 14</t>
+          <t>Mobile accessibility check 10: Accessibility compliance check 10</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
@@ -13950,7 +13950,7 @@
     <row r="422" ht="20" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-015</t>
+          <t>TC-A11Y-011</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 15: Accessibility compliance check 15</t>
+          <t>Mobile accessibility check 11: Accessibility compliance check 11</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -13982,7 +13982,7 @@
     <row r="423" ht="20" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-016</t>
+          <t>TC-A11Y-012</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 16: Accessibility compliance check 16</t>
+          <t>Mobile accessibility check 12: Accessibility compliance check 12</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="424" ht="20" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-017</t>
+          <t>TC-A11Y-013</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 17: Accessibility compliance check 17</t>
+          <t>Mobile accessibility check 13: Accessibility compliance check 13</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -14046,7 +14046,7 @@
     <row r="425" ht="20" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-018</t>
+          <t>TC-A11Y-014</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 18: Accessibility compliance check 18</t>
+          <t>Mobile accessibility check 14: Accessibility compliance check 14</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -14078,7 +14078,7 @@
     <row r="426" ht="20" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-019</t>
+          <t>TC-A11Y-015</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 19: Accessibility compliance check 19</t>
+          <t>Mobile accessibility check 15: Accessibility compliance check 15</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -14110,7 +14110,7 @@
     <row r="427" ht="20" customHeight="1">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>TC-A11Y-020</t>
+          <t>TC-A11Y-016</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>Mobile accessibility check 20: Accessibility compliance check 20</t>
+          <t>Mobile accessibility check 16: Accessibility compliance check 16</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
@@ -14142,17 +14142,17 @@
     <row r="428" ht="20" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-001</t>
+          <t>TC-A11Y-017</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 1: Portrait to Landscape screen rotation</t>
+          <t>Mobile accessibility check 17: Accessibility compliance check 17</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -14174,17 +14174,17 @@
     <row r="429" ht="20" customHeight="1">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-002</t>
+          <t>TC-A11Y-018</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 2: Small screen 5.0 inch display layout</t>
+          <t>Mobile accessibility check 18: Accessibility compliance check 18</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -14206,17 +14206,17 @@
     <row r="430" ht="20" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-003</t>
+          <t>TC-A11Y-019</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 3: Tablet 10.0 inch split-view dashboard</t>
+          <t>Mobile accessibility check 19: Accessibility compliance check 19</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
@@ -14238,17 +14238,17 @@
     <row r="431" ht="20" customHeight="1">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-004</t>
+          <t>TC-A11Y-020</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Responsive UI</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 4: System dark mode theme adaptation</t>
+          <t>Mobile accessibility check 20: Accessibility compliance check 20</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="432" ht="20" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-005</t>
+          <t>TC-RESP-001</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 5: Display density and notch handling scenario 5</t>
+          <t>Device screen responsiveness 1: Portrait to Landscape screen rotation</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
@@ -14302,7 +14302,7 @@
     <row r="433" ht="20" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-006</t>
+          <t>TC-RESP-002</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 6: Display density and notch handling scenario 6</t>
+          <t>Device screen responsiveness 2: Small screen 5.0 inch display layout</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="434" ht="20" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-007</t>
+          <t>TC-RESP-003</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 7: Display density and notch handling scenario 7</t>
+          <t>Device screen responsiveness 3: Tablet 10.0 inch split-view dashboard</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -14366,7 +14366,7 @@
     <row r="435" ht="20" customHeight="1">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-008</t>
+          <t>TC-RESP-004</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 8: Display density and notch handling scenario 8</t>
+          <t>Device screen responsiveness 4: System dark mode theme adaptation</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
@@ -14398,7 +14398,7 @@
     <row r="436" ht="20" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-009</t>
+          <t>TC-RESP-005</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 9: Display density and notch handling scenario 9</t>
+          <t>Device screen responsiveness 5: Display density and notch handling scenario 5</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
     <row r="437" ht="20" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>TC-RESP-010</t>
+          <t>TC-RESP-006</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Device screen responsiveness 10: Display density and notch handling scenario 10</t>
+          <t>Device screen responsiveness 6: Display density and notch handling scenario 6</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
@@ -14462,22 +14462,22 @@
     <row r="438" ht="20" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-RESP-007</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive UI</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 1: App cold start time &lt; 2.5 seconds</t>
+          <t>Device screen responsiveness 7: Display density and notch handling scenario 7</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
@@ -14487,29 +14487,29 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
     <row r="439" ht="20" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-RESP-008</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive UI</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 2: App warm start time &lt; 1.0 second</t>
+          <t>Device screen responsiveness 8: Display density and notch handling scenario 8</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E439" s="3" t="inlineStr">
@@ -14519,29 +14519,29 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-003</t>
+          <t>TC-RESP-009</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive UI</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 3: 60 FPS smooth scrolling in biomarker list</t>
+          <t>Device screen responsiveness 9: Display density and notch handling scenario 9</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
@@ -14551,29 +14551,29 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
     <row r="441" ht="20" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-004</t>
+          <t>TC-RESP-010</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive UI</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 4: Memory consumption &lt; 150 MB during report parse</t>
+          <t>Device screen responsiveness 10: Display density and notch handling scenario 10</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
@@ -14583,14 +14583,14 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
     <row r="442" ht="20" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-005</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 5: Performance metrics validation 5</t>
+          <t>Mobile performance benchmark 1: App cold start time &lt; 2.5 seconds</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
@@ -14622,7 +14622,7 @@
     <row r="443" ht="20" customHeight="1">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-006</t>
+          <t>TC-PERF-002</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -14632,12 +14632,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 6: Performance metrics validation 6</t>
+          <t>Mobile performance benchmark 2: App warm start time &lt; 1.0 second</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E443" s="3" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="444" ht="20" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-007</t>
+          <t>TC-PERF-003</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 7: Performance metrics validation 7</t>
+          <t>Mobile performance benchmark 3: 60 FPS smooth scrolling in biomarker list</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
@@ -14686,7 +14686,7 @@
     <row r="445" ht="20" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-008</t>
+          <t>TC-PERF-004</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 8: Performance metrics validation 8</t>
+          <t>Mobile performance benchmark 4: Memory consumption &lt; 150 MB during report parse</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E445" s="3" t="inlineStr">
@@ -14718,7 +14718,7 @@
     <row r="446" ht="20" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-009</t>
+          <t>TC-PERF-005</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 9: Performance metrics validation 9</t>
+          <t>Mobile performance benchmark 5: Performance metrics validation 5</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
@@ -14750,7 +14750,7 @@
     <row r="447" ht="20" customHeight="1">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-010</t>
+          <t>TC-PERF-006</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 10: Performance metrics validation 10</t>
+          <t>Mobile performance benchmark 6: Performance metrics validation 6</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
@@ -14782,7 +14782,7 @@
     <row r="448" ht="20" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-011</t>
+          <t>TC-PERF-007</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 11: Performance metrics validation 11</t>
+          <t>Mobile performance benchmark 7: Performance metrics validation 7</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="449" ht="20" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-012</t>
+          <t>TC-PERF-008</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 12: Performance metrics validation 12</t>
+          <t>Mobile performance benchmark 8: Performance metrics validation 8</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
@@ -14846,7 +14846,7 @@
     <row r="450" ht="20" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-013</t>
+          <t>TC-PERF-009</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 13: Performance metrics validation 13</t>
+          <t>Mobile performance benchmark 9: Performance metrics validation 9</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -14878,7 +14878,7 @@
     <row r="451" ht="20" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-014</t>
+          <t>TC-PERF-010</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 14: Performance metrics validation 14</t>
+          <t>Mobile performance benchmark 10: Performance metrics validation 10</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -14910,7 +14910,7 @@
     <row r="452" ht="20" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-015</t>
+          <t>TC-PERF-011</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 15: Performance metrics validation 15</t>
+          <t>Mobile performance benchmark 11: Performance metrics validation 11</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="453" ht="20" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-016</t>
+          <t>TC-PERF-012</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 16: Performance metrics validation 16</t>
+          <t>Mobile performance benchmark 12: Performance metrics validation 12</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="454" ht="20" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-017</t>
+          <t>TC-PERF-013</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 17: Performance metrics validation 17</t>
+          <t>Mobile performance benchmark 13: Performance metrics validation 13</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -15006,7 +15006,7 @@
     <row r="455" ht="20" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-018</t>
+          <t>TC-PERF-014</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 18: Performance metrics validation 18</t>
+          <t>Mobile performance benchmark 14: Performance metrics validation 14</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -15038,7 +15038,7 @@
     <row r="456" ht="20" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-019</t>
+          <t>TC-PERF-015</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 19: Performance metrics validation 19</t>
+          <t>Mobile performance benchmark 15: Performance metrics validation 15</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -15070,7 +15070,7 @@
     <row r="457" ht="20" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-020</t>
+          <t>TC-PERF-016</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>Mobile performance benchmark 20: Performance metrics validation 20</t>
+          <t>Mobile performance benchmark 16: Performance metrics validation 16</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -15102,22 +15102,22 @@
     <row r="458" ht="20" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-001</t>
+          <t>TC-PERF-017</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 1: Full cycle: Register -&gt; Upload CBC Report -&gt; Inspect Flagged Hemoglobin -&gt; Chat</t>
+          <t>Mobile performance benchmark 17: Performance metrics validation 17</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
@@ -15127,29 +15127,29 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
     </row>
     <row r="459" ht="20" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-002</t>
+          <t>TC-PERF-018</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 2: Full cycle: Guest Login -&gt; Upload Lipid Panel -&gt; Check Cholesterol Trends</t>
+          <t>Mobile performance benchmark 18: Performance metrics validation 18</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E459" s="3" t="inlineStr">
@@ -15159,29 +15159,29 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
     </row>
     <row r="460" ht="20" customHeight="1">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-003</t>
+          <t>TC-PERF-019</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 3: Full cycle: Upload Radiology Scan -&gt; Verify Impression Summary Extraction</t>
+          <t>Mobile performance benchmark 19: Performance metrics validation 19</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
@@ -15191,29 +15191,29 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
     </row>
     <row r="461" ht="20" customHeight="1">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-004</t>
+          <t>TC-PERF-020</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 4: Full cycle: Profile Update -&gt; Set Diabetes Baseline -&gt; Verify Reference Range Adjustment</t>
+          <t>Mobile performance benchmark 20: Performance metrics validation 20</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E461" s="3" t="inlineStr">
@@ -15223,14 +15223,14 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.01s</t>
         </is>
       </c>
     </row>
     <row r="462" ht="20" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-005</t>
+          <t>TC-REGR-001</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 5: Clinical E2E scenario regression verification 5</t>
+          <t>End-to-End clinical workflow regression scenario 1: Full cycle: Register -&gt; Upload CBC Report -&gt; Inspect Flagged Hemoglobin -&gt; Chat</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
@@ -15262,7 +15262,7 @@
     <row r="463" ht="20" customHeight="1">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-006</t>
+          <t>TC-REGR-002</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -15272,12 +15272,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 6: Clinical E2E scenario regression verification 6</t>
+          <t>End-to-End clinical workflow regression scenario 2: Full cycle: Guest Login -&gt; Upload Lipid Panel -&gt; Check Cholesterol Trends</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="464" ht="20" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-007</t>
+          <t>TC-REGR-003</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 7: Clinical E2E scenario regression verification 7</t>
+          <t>End-to-End clinical workflow regression scenario 3: Full cycle: Upload Radiology Scan -&gt; Verify Impression Summary Extraction</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
@@ -15326,7 +15326,7 @@
     <row r="465" ht="20" customHeight="1">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-008</t>
+          <t>TC-REGR-004</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -15336,12 +15336,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 8: Clinical E2E scenario regression verification 8</t>
+          <t>End-to-End clinical workflow regression scenario 4: Full cycle: Profile Update -&gt; Set Diabetes Baseline -&gt; Verify Reference Range Adjustment</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E465" s="3" t="inlineStr">
@@ -15358,7 +15358,7 @@
     <row r="466" ht="20" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-009</t>
+          <t>TC-REGR-005</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 9: Clinical E2E scenario regression verification 9</t>
+          <t>End-to-End clinical workflow regression scenario 5: Clinical E2E scenario regression verification 5</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
@@ -15390,7 +15390,7 @@
     <row r="467" ht="20" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-010</t>
+          <t>TC-REGR-006</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 10: Clinical E2E scenario regression verification 10</t>
+          <t>End-to-End clinical workflow regression scenario 6: Clinical E2E scenario regression verification 6</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
     <row r="468" ht="20" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-011</t>
+          <t>TC-REGR-007</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 11: Clinical E2E scenario regression verification 11</t>
+          <t>End-to-End clinical workflow regression scenario 7: Clinical E2E scenario regression verification 7</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="469" ht="20" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-012</t>
+          <t>TC-REGR-008</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 12: Clinical E2E scenario regression verification 12</t>
+          <t>End-to-End clinical workflow regression scenario 8: Clinical E2E scenario regression verification 8</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
@@ -15486,7 +15486,7 @@
     <row r="470" ht="20" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-013</t>
+          <t>TC-REGR-009</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 13: Clinical E2E scenario regression verification 13</t>
+          <t>End-to-End clinical workflow regression scenario 9: Clinical E2E scenario regression verification 9</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
@@ -15518,7 +15518,7 @@
     <row r="471" ht="20" customHeight="1">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-014</t>
+          <t>TC-REGR-010</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 14: Clinical E2E scenario regression verification 14</t>
+          <t>End-to-End clinical workflow regression scenario 10: Clinical E2E scenario regression verification 10</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
@@ -15550,7 +15550,7 @@
     <row r="472" ht="20" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-015</t>
+          <t>TC-REGR-011</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 15: Clinical E2E scenario regression verification 15</t>
+          <t>End-to-End clinical workflow regression scenario 11: Clinical E2E scenario regression verification 11</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
@@ -15582,7 +15582,7 @@
     <row r="473" ht="20" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-016</t>
+          <t>TC-REGR-012</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 16: Clinical E2E scenario regression verification 16</t>
+          <t>End-to-End clinical workflow regression scenario 12: Clinical E2E scenario regression verification 12</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="474" ht="20" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-017</t>
+          <t>TC-REGR-013</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 17: Clinical E2E scenario regression verification 17</t>
+          <t>End-to-End clinical workflow regression scenario 13: Clinical E2E scenario regression verification 13</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -15646,7 +15646,7 @@
     <row r="475" ht="20" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-018</t>
+          <t>TC-REGR-014</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 18: Clinical E2E scenario regression verification 18</t>
+          <t>End-to-End clinical workflow regression scenario 14: Clinical E2E scenario regression verification 14</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -15678,7 +15678,7 @@
     <row r="476" ht="20" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-019</t>
+          <t>TC-REGR-015</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 19: Clinical E2E scenario regression verification 19</t>
+          <t>End-to-End clinical workflow regression scenario 15: Clinical E2E scenario regression verification 15</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
     <row r="477" ht="20" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-020</t>
+          <t>TC-REGR-016</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 20: Clinical E2E scenario regression verification 20</t>
+          <t>End-to-End clinical workflow regression scenario 16: Clinical E2E scenario regression verification 16</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
     <row r="478" ht="20" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-021</t>
+          <t>TC-REGR-017</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 21: Clinical E2E scenario regression verification 21</t>
+          <t>End-to-End clinical workflow regression scenario 17: Clinical E2E scenario regression verification 17</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="479" ht="20" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-022</t>
+          <t>TC-REGR-018</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 22: Clinical E2E scenario regression verification 22</t>
+          <t>End-to-End clinical workflow regression scenario 18: Clinical E2E scenario regression verification 18</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
     <row r="480" ht="20" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-023</t>
+          <t>TC-REGR-019</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 23: Clinical E2E scenario regression verification 23</t>
+          <t>End-to-End clinical workflow regression scenario 19: Clinical E2E scenario regression verification 19</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
@@ -15838,7 +15838,7 @@
     <row r="481" ht="20" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-024</t>
+          <t>TC-REGR-020</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 24: Clinical E2E scenario regression verification 24</t>
+          <t>End-to-End clinical workflow regression scenario 20: Clinical E2E scenario regression verification 20</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
@@ -15870,7 +15870,7 @@
     <row r="482" ht="20" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-025</t>
+          <t>TC-REGR-021</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 25: Clinical E2E scenario regression verification 25</t>
+          <t>End-to-End clinical workflow regression scenario 21: Clinical E2E scenario regression verification 21</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -15902,7 +15902,7 @@
     <row r="483" ht="20" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-026</t>
+          <t>TC-REGR-022</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 26: Clinical E2E scenario regression verification 26</t>
+          <t>End-to-End clinical workflow regression scenario 22: Clinical E2E scenario regression verification 22</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="484" ht="20" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-027</t>
+          <t>TC-REGR-023</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 27: Clinical E2E scenario regression verification 27</t>
+          <t>End-to-End clinical workflow regression scenario 23: Clinical E2E scenario regression verification 23</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -15966,7 +15966,7 @@
     <row r="485" ht="20" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-028</t>
+          <t>TC-REGR-024</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 28: Clinical E2E scenario regression verification 28</t>
+          <t>End-to-End clinical workflow regression scenario 24: Clinical E2E scenario regression verification 24</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
     <row r="486" ht="20" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-029</t>
+          <t>TC-REGR-025</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 29: Clinical E2E scenario regression verification 29</t>
+          <t>End-to-End clinical workflow regression scenario 25: Clinical E2E scenario regression verification 25</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -16030,7 +16030,7 @@
     <row r="487" ht="20" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-030</t>
+          <t>TC-REGR-026</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 30: Clinical E2E scenario regression verification 30</t>
+          <t>End-to-End clinical workflow regression scenario 26: Clinical E2E scenario regression verification 26</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
@@ -16062,7 +16062,7 @@
     <row r="488" ht="20" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-031</t>
+          <t>TC-REGR-027</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 31: Clinical E2E scenario regression verification 31</t>
+          <t>End-to-End clinical workflow regression scenario 27: Clinical E2E scenario regression verification 27</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="489" ht="20" customHeight="1">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-032</t>
+          <t>TC-REGR-028</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 32: Clinical E2E scenario regression verification 32</t>
+          <t>End-to-End clinical workflow regression scenario 28: Clinical E2E scenario regression verification 28</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
@@ -16126,7 +16126,7 @@
     <row r="490" ht="20" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-033</t>
+          <t>TC-REGR-029</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 33: Clinical E2E scenario regression verification 33</t>
+          <t>End-to-End clinical workflow regression scenario 29: Clinical E2E scenario regression verification 29</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -16158,7 +16158,7 @@
     <row r="491" ht="20" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-034</t>
+          <t>TC-REGR-030</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 34: Clinical E2E scenario regression verification 34</t>
+          <t>End-to-End clinical workflow regression scenario 30: Clinical E2E scenario regression verification 30</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
@@ -16190,7 +16190,7 @@
     <row r="492" ht="20" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-035</t>
+          <t>TC-REGR-031</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 35: Clinical E2E scenario regression verification 35</t>
+          <t>End-to-End clinical workflow regression scenario 31: Clinical E2E scenario regression verification 31</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -16222,7 +16222,7 @@
     <row r="493" ht="20" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-036</t>
+          <t>TC-REGR-032</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 36: Clinical E2E scenario regression verification 36</t>
+          <t>End-to-End clinical workflow regression scenario 32: Clinical E2E scenario regression verification 32</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="494" ht="20" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-037</t>
+          <t>TC-REGR-033</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 37: Clinical E2E scenario regression verification 37</t>
+          <t>End-to-End clinical workflow regression scenario 33: Clinical E2E scenario regression verification 33</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="495" ht="20" customHeight="1">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-038</t>
+          <t>TC-REGR-034</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 38: Clinical E2E scenario regression verification 38</t>
+          <t>End-to-End clinical workflow regression scenario 34: Clinical E2E scenario regression verification 34</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -16318,7 +16318,7 @@
     <row r="496" ht="20" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-039</t>
+          <t>TC-REGR-035</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 39: Clinical E2E scenario regression verification 39</t>
+          <t>End-to-End clinical workflow regression scenario 35: Clinical E2E scenario regression verification 35</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -16350,7 +16350,7 @@
     <row r="497" ht="20" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-040</t>
+          <t>TC-REGR-036</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 40: Clinical E2E scenario regression verification 40</t>
+          <t>End-to-End clinical workflow regression scenario 36: Clinical E2E scenario regression verification 36</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -16382,7 +16382,7 @@
     <row r="498" ht="20" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-041</t>
+          <t>TC-REGR-037</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 41: Clinical E2E scenario regression verification 41</t>
+          <t>End-to-End clinical workflow regression scenario 37: Clinical E2E scenario regression verification 37</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="499" ht="20" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-042</t>
+          <t>TC-REGR-038</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 42: Clinical E2E scenario regression verification 42</t>
+          <t>End-to-End clinical workflow regression scenario 38: Clinical E2E scenario regression verification 38</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
@@ -16446,7 +16446,7 @@
     <row r="500" ht="20" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-043</t>
+          <t>TC-REGR-039</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 43: Clinical E2E scenario regression verification 43</t>
+          <t>End-to-End clinical workflow regression scenario 39: Clinical E2E scenario regression verification 39</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
     <row r="501" ht="20" customHeight="1">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-044</t>
+          <t>TC-REGR-040</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 44: Clinical E2E scenario regression verification 44</t>
+          <t>End-to-End clinical workflow regression scenario 40: Clinical E2E scenario regression verification 40</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -16510,7 +16510,7 @@
     <row r="502" ht="20" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-045</t>
+          <t>TC-REGR-041</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 45: Clinical E2E scenario regression verification 45</t>
+          <t>End-to-End clinical workflow regression scenario 41: Clinical E2E scenario regression verification 41</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -16542,7 +16542,7 @@
     <row r="503" ht="20" customHeight="1">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-046</t>
+          <t>TC-REGR-042</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 46: Clinical E2E scenario regression verification 46</t>
+          <t>End-to-End clinical workflow regression scenario 42: Clinical E2E scenario regression verification 42</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
@@ -16574,7 +16574,7 @@
     <row r="504" ht="20" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-047</t>
+          <t>TC-REGR-043</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 47: Clinical E2E scenario regression verification 47</t>
+          <t>End-to-End clinical workflow regression scenario 43: Clinical E2E scenario regression verification 43</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -16606,7 +16606,7 @@
     <row r="505" ht="20" customHeight="1">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-048</t>
+          <t>TC-REGR-044</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 48: Clinical E2E scenario regression verification 48</t>
+          <t>End-to-End clinical workflow regression scenario 44: Clinical E2E scenario regression verification 44</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -16638,7 +16638,7 @@
     <row r="506" ht="20" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>TC-REGR-049</t>
+          <t>TC-REGR-045</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>End-to-End clinical workflow regression scenario 49: Clinical E2E scenario regression verification 49</t>
+          <t>End-to-End clinical workflow regression scenario 45: Clinical E2E scenario regression verification 45</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -16670,30 +16670,158 @@
     <row r="507" ht="20" customHeight="1">
       <c r="A507" s="2" t="inlineStr">
         <is>
+          <t>TC-REGR-046</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>End-to-End clinical workflow regression scenario 46: Clinical E2E scenario regression verification 46</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="20" customHeight="1">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>TC-REGR-047</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>End-to-End clinical workflow regression scenario 47: Clinical E2E scenario regression verification 47</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="20" customHeight="1">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>TC-REGR-048</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>End-to-End clinical workflow regression scenario 48: Clinical E2E scenario regression verification 48</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="20" customHeight="1">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>TC-REGR-049</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>End-to-End clinical workflow regression scenario 49: Clinical E2E scenario regression verification 49</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>0.00s</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="20" customHeight="1">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
           <t>TC-REGR-050</t>
         </is>
       </c>
-      <c r="B507" s="2" t="inlineStr">
+      <c r="B511" s="2" t="inlineStr">
         <is>
           <t>Regression Suite</t>
         </is>
       </c>
-      <c r="C507" s="2" t="inlineStr">
+      <c r="C511" s="2" t="inlineStr">
         <is>
           <t>End-to-End clinical workflow regression scenario 50: Clinical E2E scenario regression verification 50</t>
         </is>
       </c>
-      <c r="D507" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E507" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="F507" s="2" t="inlineStr">
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
         <is>
           <t>0.00s</t>
         </is>
